--- a/outputs/monitor_xlsx/20260420.xlsx
+++ b/outputs/monitor_xlsx/20260420.xlsx
@@ -544,10 +544,6 @@
           <t>+0.42%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.74%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.47%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.09%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.41%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.28%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+0.45%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+7.95%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+3.15%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>43.46億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>341.14億</t>
@@ -811,7 +774,6 @@
           <t>-20.31億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-56.14億</t>
@@ -822,8 +784,6 @@
           <t>-280.68億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>106.93%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>137.82%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-25.27億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7924口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10089口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-30.95億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-45.99億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2101,6 +2045,165 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11656</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-45</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6186</v>
+      </c>
+      <c r="I18" t="n">
+        <v>170</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1438</v>
+      </c>
+      <c r="K18" t="n">
+        <v>132</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7672</v>
+      </c>
+      <c r="M18" t="n">
+        <v>36942</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400909</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>678</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9523</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-23289</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-238</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26348</v>
+      </c>
+      <c r="K19" t="n">
+        <v>109</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34420</v>
+      </c>
+      <c r="M19" t="n">
+        <v>175202</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393731</v>
+      </c>
+      <c r="O19" t="n">
+        <v>21.47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>796</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17335</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>663</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3226</v>
+      </c>
+      <c r="I20" t="n">
+        <v>323</v>
+      </c>
+      <c r="J20" t="n">
+        <v>808</v>
+      </c>
+      <c r="K20" t="n">
+        <v>262</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9911</v>
+      </c>
+      <c r="M20" t="n">
+        <v>43856</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160558</v>
+      </c>
+      <c r="O20" t="n">
+        <v>31.44</v>
       </c>
     </row>
   </sheetData>
